--- a/stories/arbres/ATOM-FAM.VER.001-05.xlsx
+++ b/stories/arbres/ATOM-FAM.VER.001-05.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>William joue dans le salon. Il veut poser son verre. Le verre glisse. L'eau tombe sur le tapis. William a le ventre serré. Il va vers papa. William dit : papa, le verre est tombé. J'ai fait tomber l'eau. Papa s'approche. Papa dit : merci de raconter. On essuie ensemble. William prend le torchon. Le tapis redevient sec. Plus tard, William est dans la cuisine. Il attrape le saladier. Le saladier glisse. De la farine tombe. William va vers maman. Il dit : maman, j'ai fait tomber la farine. Maman dit : merci de raconter. On ramasse ensemble. Même leçon, autre pièce. On raconte à papa ou maman. C'est comme ça.</t>
+          <t>William joue dans le salon. Il veut poser son verre. Le verre glisse. L'eau tombe sur le tapis. William a le ventre serré. Il va vers papa. Papa, le verre est tombé. J'ai fait tomber l'eau. Papa s'approche. Merci de raconter. On essuie ensemble. William prend le torchon. Le tapis redevient sec. Plus tard, William est dans la cuisine. Il attrape le saladier. Le saladier glisse. De la farine tombe. William va vers maman. Maman, j'ai fait tomber la farine. Merci de raconter. On ramasse ensemble. Même leçon, autre pièce. On raconte à papa ou maman. C'est comme ça.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,16 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|William joue dans le salon. Il veut poser son verre. Le verre glisse. L'eau tombe sur le tapis. William a le ventre serré. Il va vers papa.
+enfant-m|Papa, le verre est tombé. J'ai fait tomber l'eau. Papa s'approche.
+papa|Merci de raconter. On essuie ensemble.
+narrateur|William prend le torchon. Le tapis redevient sec. Plus tard, William est dans la cuisine. Il attrape le saladier. Le saladier glisse. De la farine tombe. William va vers maman.
+narrateur|Maman, j'ai fait tomber la farine.
+maman|Merci de raconter. On ramasse ensemble. Même leçon, autre pièce. On raconte à papa ou maman. C'est comme ça.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1491,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|L'eau est tombée. Que fait William ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1664,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|William a raconté. Papa a écouté. Maman a écouté. Ensemble, ils ont ramassé.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1831,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Le sol est propre. William se lave les mains.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1998,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2038,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-FAM.VER.001-05.xlsx
+++ b/stories/arbres/ATOM-FAM.VER.001-05.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1315,6 +1320,7 @@
 maman|Merci de raconter. On ramasse ensemble. Même leçon, autre pièce. On raconte à papa ou maman. C'est comme ça.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1498,6 +1504,7 @@
           <t>narrateur|L'eau est tombée. Que fait William ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1669,6 +1676,7 @@
           <t>narrateur|William a raconté. Papa a écouté. Maman a écouté. Ensemble, ils ont ramassé.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1836,6 +1844,7 @@
           <t>narrateur|Le sol est propre. William se lave les mains.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2003,6 +2012,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2021,7 +2031,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2045,6 +2055,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2059,7 +2083,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2246,6 +2270,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-FAM.VER.001-05.xlsx
+++ b/stories/arbres/ATOM-FAM.VER.001-05.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>William raconte à papa et maman</t>
+          <t>Raphaël raconte à papa et maman</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Raphaël fait tomber de l'eau au salon. Il raconte à papa. Plus tard, de la farine tombe. Il raconte à maman.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>William joue dans le salon. Il veut poser son verre. Le verre glisse. L'eau tombe sur le tapis. William a le ventre serré. Il va vers papa. Papa, le verre est tombé. J'ai fait tomber l'eau. Papa s'approche. Merci de raconter. On essuie ensemble. William prend le torchon. Le tapis redevient sec. Plus tard, William est dans la cuisine. Il attrape le saladier. Le saladier glisse. De la farine tombe. William va vers maman. Maman, j'ai fait tomber la farine. Merci de raconter. On ramasse ensemble. Même leçon, autre pièce. On raconte à papa ou maman. C'est comme ça.</t>
+          <t>Les chaussettes sèchent sur le radiateur. Elles sentent la laine chaude. La pluie tapote la vitre. Ça fait des petits traits gris. Un livre de bateau est ouvert. La page montre une voile blanche. Le tapis du salon est épais. Tu as vu la voile, Raphaël ? Oui, papa. Elle est blanche. Les chaussettes sont presque sèches. Tu les as senties ? Oui. Elles sont chaudes. En ce moment, Raphaël feuillette le livre. Il a un verre d'eau près du livre. Il veut poser son verre. Le verre glisse. L'eau tombe sur le tapis. Ça fait une tache foncée. Raphaël a le ventre serré. Il va vers papa. Papa, le verre est tombé. J'ai fait tomber l'eau. Je t'écoute, Raphaël. Merci de raconter. On essuie ensemble. Tu as fait du bon travail. Tu veux le torchon ? Oui, papa. Raphaël prend le torchon. Le tapis redevient sec, presque. On pose le verre plus loin, d'accord ? D'accord. Plus tard, Raphaël est dans la cuisine. Ça sent le pain. Un saladier attend près de la farine. Raphaël veut aider maman. Il attrape le saladier. Le saladier glisse. De la farine tombe. Ça fait un nuage blanc. Raphaël va vers maman. Maman, j'ai fait tomber la farine. J'ai raconté. Je t'écoute. Merci de raconter. On ramasse ensemble. On raconte à papa ou maman. C'est comme ça. Bravo, Raphaël. C'est du bon travail. Tu veux la petite balayette ? Oui, maman. Ils ramassent la farine. Le sol redevient clair. Tu as raconté deux fois, aujourd'hui. Oui. L'eau, puis la farine. Chaque fois, on raconte. Tu veux un bout de pain, maintenant ? Oui. Un bout tout petit. Le pain est tiède sous les doigts. La pluie tapote encore la vitre.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,15 +1324,78 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|William joue dans le salon. Il veut poser son verre. Le verre glisse. L'eau tombe sur le tapis. William a le ventre serré. Il va vers papa.
-enfant-m|Papa, le verre est tombé. J'ai fait tomber l'eau. Papa s'approche.
-papa|Merci de raconter. On essuie ensemble.
-narrateur|William prend le torchon. Le tapis redevient sec. Plus tard, William est dans la cuisine. Il attrape le saladier. Le saladier glisse. De la farine tombe. William va vers maman.
-narrateur|Maman, j'ai fait tomber la farine.
-maman|Merci de raconter. On ramasse ensemble. Même leçon, autre pièce. On raconte à papa ou maman. C'est comme ça.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|Les chaussettes sèchent sur le radiateur.
+narrateur|Elles sentent la laine chaude.
+narrateur|La pluie tapote la vitre.
+narrateur|Ça fait des petits traits gris.
+narrateur|Un livre de bateau est ouvert.
+narrateur|La page montre une voile blanche.
+narrateur|Le tapis du salon est épais.
+papa|Tu as vu la voile, Raphaël ?
+enfant-m|Oui, papa.
+enfant-m|Elle est blanche.
+papa|Les chaussettes sont presque sèches.
+papa|Tu les as senties ?
+enfant-m|Oui.
+enfant-m|Elles sont chaudes.
+narrateur|En ce moment, Raphaël feuillette le livre.
+narrateur|Il a un verre d'eau près du livre.
+narrateur|Il veut poser son verre.
+narrateur|Le verre glisse.
+narrateur|L'eau tombe sur le tapis.
+narrateur|Ça fait une tache foncée.
+narrateur|Raphaël a le ventre serré.
+narrateur|Il va vers papa.
+enfant-m|Papa, le verre est tombé.
+enfant-m|J'ai fait tomber l'eau.
+papa|Je t'écoute, Raphaël.
+papa|Merci de raconter.
+papa|On essuie ensemble.
+papa|Tu as fait du bon travail.
+papa|Tu veux le torchon ?
+enfant-m|Oui, papa.
+narrateur|Raphaël prend le torchon.
+narrateur|Le tapis redevient sec, presque.
+papa|On pose le verre plus loin, d'accord ?
+enfant-m|D'accord.
+narrateur|Plus tard, Raphaël est dans la cuisine.
+narrateur|Ça sent le pain.
+narrateur|Un saladier attend près de la farine.
+narrateur|Raphaël veut aider maman.
+narrateur|Il attrape le saladier.
+narrateur|Le saladier glisse.
+narrateur|De la farine tombe.
+narrateur|Ça fait un nuage blanc.
+narrateur|Raphaël va vers maman.
+enfant-m|Maman, j'ai fait tomber la farine.
+enfant-m|J'ai raconté.
+maman|Je t'écoute.
+maman|Merci de raconter.
+maman|On ramasse ensemble.
+maman|On raconte à papa ou maman.
+maman|C'est comme ça.
+maman|Bravo, Raphaël.
+maman|C'est du bon travail.
+maman|Tu veux la petite balayette ?
+enfant-m|Oui, maman.
+narrateur|Ils ramassent la farine.
+narrateur|Le sol redevient clair.
+papa|Tu as raconté deux fois, aujourd'hui.
+enfant-m|Oui.
+enfant-m|L'eau, puis la farine.
+papa|Chaque fois, on raconte.
+maman|Tu veux un bout de pain, maintenant ?
+enfant-m|Oui.
+enfant-m|Un bout tout petit.
+narrateur|Le pain est tiède sous les doigts.
+narrateur|La pluie tapote encore la vitre.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>pluie_vitre,verre_eau</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1345,7 +1420,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>L'eau est tombée. Que fait William ?</t>
+          <t>L'eau est tombée. Que fait Raphaël ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1501,7 +1576,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|L'eau est tombée. Que fait William ?</t>
+          <t>narrateur|L'eau est tombée.
+narrateur|Que fait Raphaël ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1529,7 +1605,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>William a raconté. Papa a écouté. Maman a écouté. Ensemble, ils ont ramassé.</t>
+          <t>Raphaël a raconté. Papa a écouté. Maman a écouté. Ensemble, ils ont ramassé. Merci d'avoir raconté. On raconte à papa ou maman. Bravo, Raphaël. J'ai raconté. Deux fois. Oui. C'est du bon travail.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1673,7 +1749,17 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|William a raconté. Papa a écouté. Maman a écouté. Ensemble, ils ont ramassé.</t>
+          <t>narrateur|Raphaël a raconté.
+narrateur|Papa a écouté.
+narrateur|Maman a écouté.
+narrateur|Ensemble, ils ont ramassé.
+papa|Merci d'avoir raconté.
+maman|On raconte à papa ou maman.
+papa|Bravo, Raphaël.
+enfant-m|J'ai raconté.
+enfant-m|Deux fois.
+maman|Oui.
+maman|C'est du bon travail.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1701,7 +1787,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Le sol est propre. William se lave les mains.</t>
+          <t>Le sol est propre. Raphaël se lave les mains. L'eau est tiède, hein ? Oui. La farine part. Le livre de bateau est encore ouvert. Tu veux regarder la voile ? Oui. La voile blanche. La pluie tapote encore, plus doucement.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1841,7 +1927,16 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Le sol est propre. William se lave les mains.</t>
+          <t>narrateur|Le sol est propre.
+narrateur|Raphaël se lave les mains.
+maman|L'eau est tiède, hein ?
+enfant-m|Oui.
+enfant-m|La farine part.
+papa|Le livre de bateau est encore ouvert.
+papa|Tu veux regarder la voile ?
+enfant-m|Oui.
+enfant-m|La voile blanche.
+narrateur|La pluie tapote encore, plus doucement.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1869,7 +1964,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai raconté. Papa et maman ont écouté. Bravo. Tu as fait du bon travail. Les chaussettes sont sèches, maintenant. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2009,7 +2104,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai raconté.
+enfant-m|Papa et maman ont écouté.
+papa|Bravo.
+maman|Tu as fait du bon travail.
+narrateur|Les chaussettes sont sèches, maintenant.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2031,7 +2131,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2069,6 +2169,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-FAM.VER.001-05.xlsx
+++ b/stories/arbres/ATOM-FAM.VER.001-05.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Les chaussettes sèchent sur le radiateur. Elles sentent la laine chaude. La pluie tapote la vitre. Ça fait des petits traits gris. Un livre de bateau est ouvert. La page montre une voile blanche. Le tapis du salon est épais. Tu as vu la voile, Raphaël ? Oui, papa. Elle est blanche. Les chaussettes sont presque sèches. Tu les as senties ? Oui. Elles sont chaudes. En ce moment, Raphaël feuillette le livre. Il a un verre d'eau près du livre. Il veut poser son verre. Le verre glisse. L'eau tombe sur le tapis. Ça fait une tache foncée. Raphaël a le ventre serré. Il va vers papa. Papa, le verre est tombé. J'ai fait tomber l'eau. Je t'écoute, Raphaël. Merci de raconter. On essuie ensemble. Tu as fait du bon travail. Tu veux le torchon ? Oui, papa. Raphaël prend le torchon. Le tapis redevient sec, presque. On pose le verre plus loin, d'accord ? D'accord. Plus tard, Raphaël est dans la cuisine. Ça sent le pain. Un saladier attend près de la farine. Raphaël veut aider maman. Il attrape le saladier. Le saladier glisse. De la farine tombe. Ça fait un nuage blanc. Raphaël va vers maman. Maman, j'ai fait tomber la farine. J'ai raconté. Je t'écoute. Merci de raconter. On ramasse ensemble. On raconte à papa ou maman. C'est comme ça. Bravo, Raphaël. C'est du bon travail. Tu veux la petite balayette ? Oui, maman. Ils ramassent la farine. Le sol redevient clair. Tu as raconté deux fois, aujourd'hui. Oui. L'eau, puis la farine. Chaque fois, on raconte. Tu veux un bout de pain, maintenant ? Oui. Un bout tout petit. Le pain est tiède sous les doigts. La pluie tapote encore la vitre.</t>
+          <t>Les chaussettes sèchent sur le radiateur. Elles sentent la laine chaude. La pluie tapote la vitre. Ça fait des petits traits gris. Un livre de bateau est ouvert. La page montre une voile blanche. Le tapis du salon est épais. Tu as vu la voile, Raphaël ? Oui, papa. Elle est blanche. Les chaussettes sont presque sèches. Tu les as senties ? Oui. Elles sont chaudes. En ce moment, Raphaël feuillette le livre. Il a un verre d'eau près du livre. Il veut poser son verre. Le verre glisse. L'eau tombe sur le tapis. Ça fait une tache foncée. Raphaël a le ventre serré. Il va vers papa. Papa, le verre est tombé. J'ai fait tomber l'eau. Je t'écoute, Raphaël. Merci de raconter. On essuie ensemble. Tu veux le torchon ? Oui, papa. Raphaël prend le torchon. Le tapis redevient sec, presque. On pose le verre plus loin, d'accord ? D'accord. Plus tard, Raphaël est dans la cuisine. Ça sent le pain. Un saladier attend près de la farine. Raphaël veut aider maman. Il attrape le saladier. Le saladier glisse. De la farine tombe. Ça fait un nuage blanc. Raphaël va vers maman. Maman, j'ai fait tomber la farine. J'ai raconté. Je t'écoute. Merci de raconter. On ramasse ensemble. On raconte à papa ou maman. C'est comme ça. Bravo, Raphaël. Tu veux la petite balayette ? Oui, maman. Ils ramassent la farine. Le sol redevient clair. Tu as raconté deux fois, aujourd'hui. Oui. L'eau, puis la farine. Chaque fois, on raconte. Tu veux un bout de pain, maintenant ? Oui. Un bout tout petit. Le pain est tiède sous les doigts. La pluie tapote encore la vitre.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;William joue dans le salon. Il veut poser son verre. Le verre glisse. L'eau tombe sur le tapis. William a le ventre serré. Il va vers papa. William dit : papa, le verre est tombé. J'ai fait tomber l'eau. Papa s'approche. Papa dit : merci de &lt;emphasis level="moderate"&gt;raconter&lt;/emphasis&gt;. On essuie ensemble. William prend le torchon. Le tapis redevient sec. Plus tard, William est dans la cuisine. Il attrape le saladier. Le saladier glisse. De la farine tombe. William va vers maman. Il dit : maman, j'ai fait tomber la farine. Maman dit : merci de raconter. On ramasse ensemble. Même leçon, autre pièce. On raconte à papa ou maman. C'est comme ça.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Les chaussettes sèchent sur le radiateur. Elles sentent la laine chaude. La pluie tapote la vitre. Ça fait des petits traits gris. Un livre de bateau est ouvert. La page montre une voile blanche. Le tapis du salon est épais. Tu as vu la voile, Raphaël ? Oui, papa. Elle est blanche. Les chaussettes sont presque sèches. Tu les as senties ? Oui. Elles sont chaudes. En ce moment, Raphaël feuillette le livre. Il a un verre d'eau près du livre. Il veut poser son verre. Le verre glisse. L'eau tombe sur le tapis. Ça fait une tache foncée. Raphaël a le ventre serré. Il va vers papa. Papa, le verre est tombé. J'ai fait tomber l'eau. Je t'écoute, Raphaël. Merci de raconter. On essuie ensemble. Tu veux le torchon ? Oui, papa. Raphaël prend le torchon. Le tapis redevient sec, presque. On pose le verre plus loin, d'accord ? D'accord. Plus tard, Raphaël est dans la cuisine. Ça sent le pain. Un saladier attend près de la farine. Raphaël veut aider maman. Il attrape le saladier. Le saladier glisse. De la farine tombe. Ça fait un nuage blanc. Raphaël va vers maman. Maman, j'ai fait tomber la farine. J'ai raconté. Je t'écoute. Merci de raconter. On ramasse ensemble. On raconte à papa ou maman. C'est comme ça. Bravo, Raphaël. Tu veux la petite balayette ? Oui, maman. Ils ramassent la farine. Le sol redevient clair. Tu as raconté deux fois, aujourd'hui. Oui. L'eau, puis la farine. Chaque fois, on raconte. Tu veux un bout de pain, maintenant ? Oui. Un bout tout petit. Le pain est tiède sous les doigts. La pluie tapote encore la vitre.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1351,7 +1351,6 @@
 papa|Je t'écoute, Raphaël.
 papa|Merci de raconter.
 papa|On essuie ensemble.
-papa|Tu as fait du bon travail.
 papa|Tu veux le torchon ?
 enfant-m|Oui, papa.
 narrateur|Raphaël prend le torchon.
@@ -1375,7 +1374,6 @@
 maman|On raconte à papa ou maman.
 maman|C'est comme ça.
 maman|Bravo, Raphaël.
-maman|C'est du bon travail.
 maman|Tu veux la petite balayette ?
 enfant-m|Oui, maman.
 narrateur|Ils ramassent la farine.
@@ -1425,7 +1423,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;L'eau est tombée. Que fait William ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>L'eau est tombée. Que fait Raphaël ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1580,7 +1578,6 @@
 narrateur|Que fait Raphaël ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1605,12 +1602,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Raphaël a raconté. Papa a écouté. Maman a écouté. Ensemble, ils ont ramassé. Merci d'avoir raconté. On raconte à papa ou maman. Bravo, Raphaël. J'ai raconté. Deux fois. Oui. C'est du bon travail.</t>
+          <t>Raphaël a raconté. Papa a écouté. Maman a écouté. Ensemble, ils ont ramassé. Merci d'avoir raconté. On raconte à papa ou maman. Bravo, Raphaël. J'ai raconté. Deux fois. Oui.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;William a raconté. &lt;emphasis level="moderate"&gt;papa&lt;/emphasis&gt; a écouté. Maman a écouté. Ensemble, ils ont ramassé.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Raphaël a raconté. Papa a écouté. Maman a écouté. Ensemble, ils ont ramassé. Merci d'avoir raconté. On raconte à papa ou maman. Bravo, Raphaël. J'ai raconté. Deux fois. Oui.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1758,11 +1755,9 @@
 papa|Bravo, Raphaël.
 enfant-m|J'ai raconté.
 enfant-m|Deux fois.
-maman|Oui.
-maman|C'est du bon travail.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+maman|Oui.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1792,7 +1787,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le sol est propre. William se lave les &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt;s.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le sol est propre. Raphaël se lave les mains. L'eau est tiède, hein ? Oui. La farine part. Le livre de bateau est encore ouvert. Tu veux regarder la voile ? Oui. La voile blanche. La pluie tapote encore, plus doucement.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1939,7 +1934,6 @@
 narrateur|La pluie tapote encore, plus doucement.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1964,12 +1958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai raconté. Papa et maman ont écouté. Bravo. Tu as fait du bon travail. Les chaussettes sont sèches, maintenant. L'histoire est finie.</t>
+          <t>J'ai raconté. Papa et maman ont écouté. Bravo. Les chaussettes sont sèches, maintenant.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai raconté. Papa et maman ont écouté. Bravo. Les chaussettes sont sèches, maintenant.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2107,12 +2101,9 @@
           <t>enfant-m|J'ai raconté.
 enfant-m|Papa et maman ont écouté.
 papa|Bravo.
-maman|Tu as fait du bon travail.
-narrateur|Les chaussettes sont sèches, maintenant.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|Les chaussettes sont sèches, maintenant.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2131,7 +2122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2176,6 +2167,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-FAM.VER.001-05.xlsx
+++ b/stories/arbres/ATOM-FAM.VER.001-05.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>William, papa, maman</t>
+          <t>Raphaël, papa, maman</t>
         </is>
       </c>
     </row>
